--- a/data/output/sim_gridrnd/REL2/group_520_20/results/REL2_G7_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL2/group_520_20/results/REL2_G7_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,614 +466,702 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S03_G7_518_19_REL2</t>
+          <t>S01_G7_519_20_REL2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D2" t="n">
-        <v>28.16901408450704</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>507.1375030280463</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24.6370444891186</v>
-      </c>
-      <c r="K2" t="n">
-        <v>504.8792924657322</v>
-      </c>
-      <c r="L2" t="n">
-        <v>24.43635510951555</v>
-      </c>
-      <c r="M2" t="n">
-        <v>504.1706443916947</v>
-      </c>
-      <c r="N2" t="n">
-        <v>25.09112017462109</v>
-      </c>
-      <c r="O2" t="n">
-        <v>504.9887047968705</v>
-      </c>
-      <c r="P2" t="n">
-        <v>21.62812458068627</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>508.9489568612896</v>
-      </c>
       <c r="R2" t="n">
-        <v>22.95365661377832</v>
+        <v>508.03</v>
       </c>
       <c r="S2" t="n">
-        <v>507.3900434238091</v>
+        <v>23.54</v>
       </c>
       <c r="T2" t="n">
-        <v>24.18166840232452</v>
+        <v>518.37</v>
       </c>
       <c r="U2" t="n">
-        <v>509.2508078207823</v>
+        <v>22.56</v>
       </c>
       <c r="V2" t="n">
-        <v>23.07710646084939</v>
+        <v>520.25</v>
       </c>
       <c r="W2" t="n">
-        <v>511.2487117867185</v>
+        <v>22.43</v>
       </c>
       <c r="X2" t="n">
-        <v>22.04247169381973</v>
+        <v>520.78</v>
       </c>
       <c r="Y2" t="n">
-        <v>512.6265711650739</v>
+        <v>24.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.89573941380288</v>
+        <v>524.1799999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>28.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>525.3200000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>29.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>522.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>31.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>520.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>29.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>520.54</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>29.19</v>
       </c>
       <c r="AJ2" t="n">
-        <v>498.55</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>501.9166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>501.9</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>501.71</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>502.5583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>504.0642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>504.61875</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>504.9166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>505.545</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>67.29374042212247</v>
+        <v>506.15</v>
       </c>
       <c r="AT2" t="n">
-        <v>58.67830140312137</v>
+        <v>508.1666666666667</v>
       </c>
       <c r="AU2" t="n">
-        <v>53.10051788824663</v>
+        <v>510.525</v>
       </c>
       <c r="AV2" t="n">
-        <v>48.95738861499866</v>
+        <v>511.69</v>
       </c>
       <c r="AW2" t="n">
-        <v>46.30511055908288</v>
+        <v>512.5583333333333</v>
       </c>
       <c r="AX2" t="n">
-        <v>45.26985921185557</v>
+        <v>514.1071428571429</v>
       </c>
       <c r="AY2" t="n">
-        <v>43.79909700481849</v>
+        <v>515.4875</v>
       </c>
       <c r="AZ2" t="n">
-        <v>42.2117512600987</v>
+        <v>516.4166666666666</v>
       </c>
       <c r="BA2" t="n">
-        <v>40.81578095540988</v>
+        <v>516.215</v>
       </c>
       <c r="BB2" t="n">
-        <v>335</v>
+        <v>68.74356333504977</v>
       </c>
       <c r="BC2" t="n">
-        <v>335</v>
+        <v>58.98733385698625</v>
       </c>
       <c r="BD2" t="n">
-        <v>335</v>
+        <v>53.27334582133921</v>
       </c>
       <c r="BE2" t="n">
-        <v>335</v>
+        <v>49.2535673834901</v>
       </c>
       <c r="BF2" t="n">
-        <v>335</v>
+        <v>48.81833600764733</v>
       </c>
       <c r="BG2" t="n">
-        <v>335</v>
+        <v>47.89090227181111</v>
       </c>
       <c r="BH2" t="n">
-        <v>335</v>
+        <v>46.92160849491415</v>
       </c>
       <c r="BI2" t="n">
-        <v>335</v>
+        <v>46.19726723519477</v>
       </c>
       <c r="BJ2" t="n">
-        <v>335</v>
+        <v>44.99265245570658</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.9545454545454546</v>
+        <v>669</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.9210526315789473</v>
+        <v>669</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.9047619047619048</v>
+        <v>669</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.8666666666666667</v>
+        <v>669</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.8235294117647058</v>
+        <v>669</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.8392857142857143</v>
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.972972972972973</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.9767441860465116</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>520.54</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>29.19</v>
       </c>
     </row>
     <row r="3">
@@ -1086,10 +1174,10 @@
         <v>521</v>
       </c>
       <c r="C3" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D3" t="n">
         <v>18</v>
-      </c>
-      <c r="D3" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E3" t="n">
         <v>521</v>
@@ -1098,1212 +1186,1377 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>85</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>531.5025316358156</v>
-      </c>
-      <c r="J3" t="n">
-        <v>26.55901432540371</v>
-      </c>
-      <c r="K3" t="n">
-        <v>522.6498228243482</v>
-      </c>
-      <c r="L3" t="n">
-        <v>23.65523973466137</v>
-      </c>
-      <c r="M3" t="n">
-        <v>519.6324110073676</v>
-      </c>
-      <c r="N3" t="n">
-        <v>23.45426043583879</v>
-      </c>
-      <c r="O3" t="n">
-        <v>515.7492100540113</v>
-      </c>
-      <c r="P3" t="n">
-        <v>22.91068029186617</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>515.5722649657708</v>
-      </c>
       <c r="R3" t="n">
-        <v>21.10229031266184</v>
+        <v>531.5</v>
       </c>
       <c r="S3" t="n">
-        <v>517.963984789187</v>
+        <v>26.56</v>
       </c>
       <c r="T3" t="n">
-        <v>21.57513970048375</v>
+        <v>522.65</v>
       </c>
       <c r="U3" t="n">
-        <v>519.2755517140927</v>
+        <v>23.66</v>
       </c>
       <c r="V3" t="n">
-        <v>20.22727834426299</v>
+        <v>519.63</v>
       </c>
       <c r="W3" t="n">
-        <v>519.2521715636676</v>
+        <v>23.45</v>
       </c>
       <c r="X3" t="n">
-        <v>19.63209559568331</v>
+        <v>515.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>519.223783145216</v>
+        <v>22.91</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.88449195816096</v>
+        <v>515.5700000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>517.96</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>21.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>519.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>20.23</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>519.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>19.63</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>519.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>19.88</v>
       </c>
       <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>512.85</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AT3" t="n">
         <v>512.9666666666667</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AU3" t="n">
         <v>513.375</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AV3" t="n">
         <v>513</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AW3" t="n">
         <v>513.2916666666666</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AX3" t="n">
         <v>513.0714285714286</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AY3" t="n">
         <v>513.30625</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AZ3" t="n">
         <v>513.3222222222222</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="BA3" t="n">
         <v>513.39</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="BB3" t="n">
         <v>78.69992058445803</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BC3" t="n">
         <v>67.17712077452825</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BD3" t="n">
         <v>59.81541920775947</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="BE3" t="n">
         <v>54.85271187461929</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BF3" t="n">
         <v>50.88801362359859</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BG3" t="n">
         <v>48.00679161135773</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BH3" t="n">
         <v>45.65372340716034</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BI3" t="n">
         <v>43.73476313155062</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BJ3" t="n">
         <v>42.05933784547731</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BK3" t="n">
         <v>324</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BL3" t="n">
         <v>324</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BM3" t="n">
         <v>324</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BN3" t="n">
         <v>324</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BO3" t="n">
         <v>324</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BP3" t="n">
         <v>324</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BQ3" t="n">
         <v>324</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BR3" t="n">
         <v>324</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BS3" t="n">
         <v>324</v>
       </c>
-      <c r="BK3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>669</v>
-      </c>
       <c r="BT3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="CD3" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="BV3" t="n">
+      <c r="CE3" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BW3" t="n">
+      <c r="CF3" t="n">
         <v>0.6896551724137931</v>
       </c>
-      <c r="BX3" t="n">
+      <c r="CG3" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BY3" t="n">
+      <c r="CH3" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BZ3" t="n">
+      <c r="CI3" t="n">
         <v>0.6949152542372882</v>
       </c>
-      <c r="CA3" t="n">
+      <c r="CJ3" t="n">
         <v>0.7101449275362319</v>
       </c>
-      <c r="CB3" t="n">
+      <c r="CK3" t="n">
         <v>0.7088607594936709</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>519.22</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>19.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S04_G7_522_20_REL2</t>
+          <t>S03_G7_518_19_REL2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>28.16901408450704</v>
       </c>
       <c r="D4" t="n">
-        <v>29.65159377316531</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>532.4434313060084</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12.5899527402947</v>
-      </c>
-      <c r="K4" t="n">
-        <v>526.7505642378387</v>
-      </c>
-      <c r="L4" t="n">
-        <v>18.22494963796721</v>
-      </c>
-      <c r="M4" t="n">
-        <v>528.028783193709</v>
-      </c>
-      <c r="N4" t="n">
-        <v>21.37829115211259</v>
-      </c>
-      <c r="O4" t="n">
-        <v>526.6779240970433</v>
-      </c>
-      <c r="P4" t="n">
-        <v>20.06444072907759</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>525.4750679578481</v>
-      </c>
       <c r="R4" t="n">
-        <v>20.80342714160295</v>
+        <v>507.14</v>
       </c>
       <c r="S4" t="n">
-        <v>521.7124502473433</v>
+        <v>24.64</v>
       </c>
       <c r="T4" t="n">
-        <v>22.12711745335268</v>
+        <v>504.88</v>
       </c>
       <c r="U4" t="n">
-        <v>520.5442246729692</v>
+        <v>24.44</v>
       </c>
       <c r="V4" t="n">
-        <v>21.96251823347154</v>
+        <v>504.17</v>
       </c>
       <c r="W4" t="n">
-        <v>520.9080035259384</v>
+        <v>25.09</v>
       </c>
       <c r="X4" t="n">
-        <v>20.44691939450675</v>
+        <v>504.99</v>
       </c>
       <c r="Y4" t="n">
-        <v>520.934531414107</v>
+        <v>21.63</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.33579412983927</v>
+        <v>508.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>22.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>507.39</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>24.18</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>509.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>511.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>22.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>512.63</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>514.825</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>516.1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>517.0875</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>517.9299999999999</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>518.4416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>518.6142857142858</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>518.6375</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>518.4833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>518.12</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>69.49959981899177</v>
+        <v>498.55</v>
       </c>
       <c r="AT4" t="n">
-        <v>58.45131877611202</v>
+        <v>501.9166666666667</v>
       </c>
       <c r="AU4" t="n">
-        <v>52.18697005718957</v>
+        <v>501.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>48.40149894373107</v>
+        <v>501.71</v>
       </c>
       <c r="AW4" t="n">
-        <v>45.2767040602069</v>
+        <v>502.5583333333333</v>
       </c>
       <c r="AX4" t="n">
-        <v>42.93043970263086</v>
+        <v>504.0642857142857</v>
       </c>
       <c r="AY4" t="n">
-        <v>41.15466065647972</v>
+        <v>504.61875</v>
       </c>
       <c r="AZ4" t="n">
-        <v>39.71404383562291</v>
+        <v>504.9166666666667</v>
       </c>
       <c r="BA4" t="n">
-        <v>38.54096002955816</v>
+        <v>505.545</v>
       </c>
       <c r="BB4" t="n">
-        <v>344</v>
+        <v>67.29374042212247</v>
       </c>
       <c r="BC4" t="n">
-        <v>344</v>
+        <v>58.67830140312137</v>
       </c>
       <c r="BD4" t="n">
-        <v>344</v>
+        <v>53.10051788824663</v>
       </c>
       <c r="BE4" t="n">
-        <v>344</v>
+        <v>48.95738861499866</v>
       </c>
       <c r="BF4" t="n">
-        <v>344</v>
+        <v>46.30511055908288</v>
       </c>
       <c r="BG4" t="n">
-        <v>344</v>
+        <v>45.26985921185557</v>
       </c>
       <c r="BH4" t="n">
-        <v>344</v>
+        <v>43.79909700481849</v>
       </c>
       <c r="BI4" t="n">
-        <v>344</v>
+        <v>42.2117512600987</v>
       </c>
       <c r="BJ4" t="n">
-        <v>344</v>
+        <v>40.81578095540988</v>
       </c>
       <c r="BK4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BL4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BM4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BN4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BO4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BP4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BQ4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BR4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BS4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.3333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.9230769230769231</v>
+        <v>669</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.8695652173913043</v>
+        <v>669</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.7878787878787878</v>
+        <v>669</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.813953488372093</v>
+        <v>669</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.8113207547169812</v>
+        <v>669</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.7936507936507936</v>
+        <v>669</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.7671232876712328</v>
+        <v>669</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.7625</v>
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.8392857142857143</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>512.63</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>22.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S01_G7_519_20_REL2</t>
+          <t>S04_G7_522_20_REL2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C5" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D5" t="n">
         <v>20</v>
       </c>
-      <c r="D5" t="n">
-        <v>29.65159377316531</v>
-      </c>
       <c r="E5" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>85.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>508.0258040414316</v>
-      </c>
-      <c r="J5" t="n">
-        <v>23.54173558481904</v>
-      </c>
-      <c r="K5" t="n">
-        <v>518.3702974986105</v>
-      </c>
-      <c r="L5" t="n">
-        <v>22.56187581189935</v>
-      </c>
-      <c r="M5" t="n">
-        <v>520.2500774884799</v>
-      </c>
-      <c r="N5" t="n">
-        <v>22.43486580739224</v>
-      </c>
-      <c r="O5" t="n">
-        <v>520.7843488225006</v>
-      </c>
-      <c r="P5" t="n">
-        <v>24.69921008343109</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>524.176547022627</v>
-      </c>
       <c r="R5" t="n">
-        <v>28.0333414676403</v>
+        <v>532.4400000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>525.3216166864164</v>
+        <v>12.59</v>
       </c>
       <c r="T5" t="n">
-        <v>29.88124231271522</v>
+        <v>526.75</v>
       </c>
       <c r="U5" t="n">
-        <v>522.3572211060675</v>
+        <v>18.22</v>
       </c>
       <c r="V5" t="n">
-        <v>31.05078628476009</v>
+        <v>528.03</v>
       </c>
       <c r="W5" t="n">
-        <v>520.6033788183095</v>
+        <v>21.38</v>
       </c>
       <c r="X5" t="n">
-        <v>29.60164949624705</v>
+        <v>526.6799999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>520.5373068751802</v>
+        <v>20.06</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.18548903768311</v>
+        <v>525.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>521.71</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>22.13</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>520.54</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>21.96</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>520.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>20.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>520.9299999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>19.34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>506.15</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>508.1666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>510.525</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>511.69</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>512.5583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>514.1071428571429</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>515.4875</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>516.4166666666666</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>516.215</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>68.74356333504977</v>
+        <v>514.825</v>
       </c>
       <c r="AT5" t="n">
-        <v>58.98733385698625</v>
+        <v>516.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>53.27334582133921</v>
+        <v>517.0875</v>
       </c>
       <c r="AV5" t="n">
-        <v>49.2535673834901</v>
+        <v>517.9299999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>48.81833600764733</v>
+        <v>518.4416666666667</v>
       </c>
       <c r="AX5" t="n">
-        <v>47.89090227181111</v>
+        <v>518.6142857142858</v>
       </c>
       <c r="AY5" t="n">
-        <v>46.92160849491415</v>
+        <v>518.6375</v>
       </c>
       <c r="AZ5" t="n">
-        <v>46.19726723519477</v>
+        <v>518.4833333333333</v>
       </c>
       <c r="BA5" t="n">
-        <v>44.99265245570658</v>
+        <v>518.12</v>
       </c>
       <c r="BB5" t="n">
-        <v>326</v>
+        <v>69.49959981899177</v>
       </c>
       <c r="BC5" t="n">
-        <v>326</v>
+        <v>58.45131877611202</v>
       </c>
       <c r="BD5" t="n">
-        <v>326</v>
+        <v>52.18697005718957</v>
       </c>
       <c r="BE5" t="n">
-        <v>326</v>
+        <v>48.40149894373107</v>
       </c>
       <c r="BF5" t="n">
-        <v>326</v>
+        <v>45.2767040602069</v>
       </c>
       <c r="BG5" t="n">
-        <v>326</v>
+        <v>42.93043970263086</v>
       </c>
       <c r="BH5" t="n">
-        <v>326</v>
+        <v>41.15466065647972</v>
       </c>
       <c r="BI5" t="n">
-        <v>326</v>
+        <v>39.71404383562291</v>
       </c>
       <c r="BJ5" t="n">
-        <v>326</v>
+        <v>38.54096002955816</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.9333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.6956521739130435</v>
+        <v>669</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.5757575757575758</v>
+        <v>669</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.7352941176470589</v>
+        <v>669</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.8529411764705882</v>
+        <v>669</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.9411764705882353</v>
+        <v>669</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.972972972972973</v>
+        <v>669</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.9767441860465116</v>
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.813953488372093</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.7936507936507936</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.7671232876712328</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>520.9299999999999</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>19.34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G7_518_21_REL2</t>
+          <t>S05_G7_519_21_REL2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C6" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D6" t="n">
         <v>21</v>
       </c>
-      <c r="D6" t="n">
-        <v>31.13417346182357</v>
-      </c>
       <c r="E6" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>526.526586930146</v>
-      </c>
-      <c r="J6" t="n">
-        <v>20.95937847942776</v>
-      </c>
-      <c r="K6" t="n">
-        <v>528.235464792224</v>
-      </c>
-      <c r="L6" t="n">
-        <v>16.95503790784606</v>
-      </c>
-      <c r="M6" t="n">
-        <v>521.7418340618472</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20.97103729044651</v>
-      </c>
-      <c r="O6" t="n">
-        <v>520.0973252695042</v>
-      </c>
-      <c r="P6" t="n">
-        <v>19.4350042996701</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>523.9342571407302</v>
-      </c>
       <c r="R6" t="n">
-        <v>20.51589024769074</v>
+        <v>546.59</v>
       </c>
       <c r="S6" t="n">
-        <v>522.6028716619478</v>
+        <v>11.02</v>
       </c>
       <c r="T6" t="n">
-        <v>25.46633900629284</v>
+        <v>536.67</v>
       </c>
       <c r="U6" t="n">
-        <v>523.2684194754348</v>
+        <v>17.27</v>
       </c>
       <c r="V6" t="n">
-        <v>23.96294726227817</v>
+        <v>528.05</v>
       </c>
       <c r="W6" t="n">
-        <v>521.9341702295727</v>
+        <v>20.52</v>
       </c>
       <c r="X6" t="n">
-        <v>23.12005300763725</v>
+        <v>521.24</v>
       </c>
       <c r="Y6" t="n">
-        <v>521.2266753996232</v>
+        <v>23.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.68828277944844</v>
+        <v>520.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>23.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>521.24</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>24.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>521.96</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>25.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>522.1900000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>25.79</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>523.42</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>24.74</v>
       </c>
       <c r="AJ6" t="n">
-        <v>514.925</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>515.2666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>515.85</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>514.96</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>515.4416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>515.9214285714286</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>516.50625</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>515.7</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>515.375</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>71.71798501770668</v>
+        <v>512.675</v>
       </c>
       <c r="AT6" t="n">
-        <v>60.60496862652618</v>
+        <v>516.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>53.90804670918804</v>
+        <v>517.4625</v>
       </c>
       <c r="AV6" t="n">
-        <v>49.14100528072254</v>
+        <v>517.0700000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>45.96643627570979</v>
+        <v>516.4083333333333</v>
       </c>
       <c r="AX6" t="n">
-        <v>45.11573495817537</v>
+        <v>515.5357142857143</v>
       </c>
       <c r="AY6" t="n">
-        <v>44.48876218706809</v>
+        <v>516.08125</v>
       </c>
       <c r="AZ6" t="n">
-        <v>42.92136220267634</v>
+        <v>516.1055555555556</v>
       </c>
       <c r="BA6" t="n">
-        <v>41.60485999255376</v>
+        <v>515.905</v>
       </c>
       <c r="BB6" t="n">
-        <v>342</v>
+        <v>72.11427996589858</v>
       </c>
       <c r="BC6" t="n">
-        <v>342</v>
+        <v>62.06244838869959</v>
       </c>
       <c r="BD6" t="n">
-        <v>342</v>
+        <v>55.80746897817532</v>
       </c>
       <c r="BE6" t="n">
-        <v>342</v>
+        <v>51.12616844630546</v>
       </c>
       <c r="BF6" t="n">
-        <v>342</v>
+        <v>47.72115111655301</v>
       </c>
       <c r="BG6" t="n">
-        <v>342</v>
+        <v>46.20133126008472</v>
       </c>
       <c r="BH6" t="n">
-        <v>342</v>
+        <v>45.01777036279673</v>
       </c>
       <c r="BI6" t="n">
-        <v>342</v>
+        <v>44.20903593186229</v>
       </c>
       <c r="BJ6" t="n">
-        <v>342</v>
+        <v>43.09496461304963</v>
       </c>
       <c r="BK6" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BL6" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BM6" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BN6" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BO6" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BP6" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BQ6" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BR6" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BS6" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BT6" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.8461538461538461</v>
+        <v>669</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.7619047619047619</v>
+        <v>669</v>
       </c>
       <c r="BW6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="CJ6" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="BX6" t="n">
-        <v>0.8387096774193549</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.8484848484848485</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.8611111111111112</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.03125</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.7954545454545454</v>
+      <c r="CK6" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>523.42</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>24.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S05_G7_519_21_REL2</t>
+          <t>S06_G7_518_21_REL2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C7" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D7" t="n">
         <v>21</v>
       </c>
-      <c r="D7" t="n">
-        <v>31.13417346182357</v>
-      </c>
       <c r="E7" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F7" t="n">
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>546.5909623382266</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11.02417986247519</v>
-      </c>
-      <c r="K7" t="n">
-        <v>536.671575037743</v>
-      </c>
-      <c r="L7" t="n">
-        <v>17.26956723035093</v>
-      </c>
-      <c r="M7" t="n">
-        <v>528.0463779369649</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20.51619970151228</v>
-      </c>
-      <c r="O7" t="n">
-        <v>521.2407891706667</v>
-      </c>
-      <c r="P7" t="n">
-        <v>23.56758141226923</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>520.5846517778465</v>
-      </c>
       <c r="R7" t="n">
-        <v>23.95850233239939</v>
+        <v>526.53</v>
       </c>
       <c r="S7" t="n">
-        <v>521.2395109897828</v>
+        <v>20.96</v>
       </c>
       <c r="T7" t="n">
-        <v>24.1161093369982</v>
+        <v>528.24</v>
       </c>
       <c r="U7" t="n">
-        <v>521.9571128076474</v>
+        <v>16.96</v>
       </c>
       <c r="V7" t="n">
-        <v>25.81938058309114</v>
+        <v>521.74</v>
       </c>
       <c r="W7" t="n">
-        <v>522.18810965819</v>
+        <v>20.97</v>
       </c>
       <c r="X7" t="n">
-        <v>25.79139075304445</v>
+        <v>520.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>523.4151356895713</v>
+        <v>19.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.74314397867683</v>
+        <v>523.9299999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>20.52</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>522.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>25.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>523.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>23.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>521.9299999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>23.12</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>521.23</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>22.69</v>
       </c>
       <c r="AJ7" t="n">
-        <v>512.675</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>516.95</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>517.4625</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>517.0700000000001</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>516.4083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>515.5357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>516.08125</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>516.1055555555556</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>515.905</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>72.11427996589858</v>
+        <v>514.925</v>
       </c>
       <c r="AT7" t="n">
-        <v>62.06244838869959</v>
+        <v>515.2666666666667</v>
       </c>
       <c r="AU7" t="n">
-        <v>55.80746897817532</v>
+        <v>515.85</v>
       </c>
       <c r="AV7" t="n">
-        <v>51.12616844630546</v>
+        <v>514.96</v>
       </c>
       <c r="AW7" t="n">
-        <v>47.72115111655301</v>
+        <v>515.4416666666667</v>
       </c>
       <c r="AX7" t="n">
-        <v>46.20133126008472</v>
+        <v>515.9214285714286</v>
       </c>
       <c r="AY7" t="n">
-        <v>45.01777036279673</v>
+        <v>516.50625</v>
       </c>
       <c r="AZ7" t="n">
-        <v>44.20903593186229</v>
+        <v>515.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>43.09496461304963</v>
+        <v>515.375</v>
       </c>
       <c r="BB7" t="n">
-        <v>344</v>
+        <v>71.71798501770668</v>
       </c>
       <c r="BC7" t="n">
-        <v>344</v>
+        <v>60.60496862652618</v>
       </c>
       <c r="BD7" t="n">
-        <v>344</v>
+        <v>53.90804670918804</v>
       </c>
       <c r="BE7" t="n">
-        <v>344</v>
+        <v>49.14100528072254</v>
       </c>
       <c r="BF7" t="n">
-        <v>344</v>
+        <v>45.96643627570979</v>
       </c>
       <c r="BG7" t="n">
-        <v>344</v>
+        <v>45.11573495817537</v>
       </c>
       <c r="BH7" t="n">
-        <v>344</v>
+        <v>44.48876218706809</v>
       </c>
       <c r="BI7" t="n">
-        <v>344</v>
+        <v>42.92136220267634</v>
       </c>
       <c r="BJ7" t="n">
-        <v>344</v>
+        <v>41.60485999255376</v>
       </c>
       <c r="BK7" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BL7" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BM7" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BN7" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BO7" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BP7" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BQ7" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BR7" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BS7" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.7333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.8823529411764706</v>
+        <v>669</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.9565217391304348</v>
+        <v>669</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.9285714285714286</v>
+        <v>669</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.8529411764705882</v>
+        <v>669</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.9736842105263158</v>
+        <v>669</v>
       </c>
       <c r="CA7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="CF7" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="CB7" t="n">
-        <v>0.9411764705882353</v>
+      <c r="CG7" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.8611111111111112</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.7954545454545454</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>521.23</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>22.69</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>521</v>
       </c>
       <c r="C8" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D8" t="n">
         <v>18</v>
-      </c>
-      <c r="D8" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E8" t="n">
         <v>521</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>524.125896968995</v>
-      </c>
-      <c r="J8" t="n">
-        <v>21.70208810842789</v>
-      </c>
-      <c r="K8" t="n">
-        <v>516.9017606767497</v>
-      </c>
-      <c r="L8" t="n">
-        <v>18.48784842480486</v>
-      </c>
-      <c r="M8" t="n">
-        <v>517.0766985526801</v>
-      </c>
-      <c r="N8" t="n">
-        <v>18.36905653249851</v>
-      </c>
-      <c r="O8" t="n">
-        <v>519.1529596543114</v>
-      </c>
-      <c r="P8" t="n">
-        <v>18.18671104301101</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>521.1078337826692</v>
-      </c>
       <c r="R8" t="n">
-        <v>16.60991094577554</v>
+        <v>524.13</v>
       </c>
       <c r="S8" t="n">
-        <v>522.6911119846873</v>
+        <v>21.7</v>
       </c>
       <c r="T8" t="n">
-        <v>18.72824355094088</v>
+        <v>516.9</v>
       </c>
       <c r="U8" t="n">
-        <v>524.5849849725781</v>
+        <v>18.49</v>
       </c>
       <c r="V8" t="n">
-        <v>20.5432347828765</v>
+        <v>517.08</v>
       </c>
       <c r="W8" t="n">
-        <v>524.1697593192539</v>
+        <v>18.37</v>
       </c>
       <c r="X8" t="n">
-        <v>21.02081881866699</v>
+        <v>519.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>523.4042186962508</v>
+        <v>18.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.09664627793083</v>
+        <v>521.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>16.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>522.6900000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>18.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>524.58</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>20.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>524.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>21.02</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>523.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>505.55</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>507.6166666666667</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>508.3375</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>509.32</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>510.425</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>511.3357142857143</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>513.60625</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>515.2222222222222</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>516.855</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>69.07240766036755</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>59.38548971667144</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>53.16647057826953</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>48.85834217408528</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>45.59763562949289</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>43.19963801341159</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>42.80713971918119</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>42.13873324515312</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>41.7883234289197</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>327</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>327</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>327</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>327</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>327</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>327</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>327</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>327</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>327</v>
       </c>
-      <c r="BK8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>669</v>
-      </c>
       <c r="BT8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.5925925925925926</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.5</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.5</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.5535714285714286</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.6379310344827587</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.7241379310344828</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.7931034482758621</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>523.4</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>22.1</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>520</v>
       </c>
       <c r="C9" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D9" t="n">
         <v>20</v>
-      </c>
-      <c r="D9" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E9" t="n">
         <v>520</v>
@@ -2574,244 +2860,277 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>531.2138609839832</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.601909273024729</v>
-      </c>
-      <c r="K9" t="n">
-        <v>522.515892052076</v>
-      </c>
-      <c r="L9" t="n">
-        <v>15.73176255070324</v>
-      </c>
-      <c r="M9" t="n">
-        <v>520.6636940951436</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14.8251530839457</v>
-      </c>
-      <c r="O9" t="n">
-        <v>521.8280359605257</v>
-      </c>
-      <c r="P9" t="n">
-        <v>17.35226159967125</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>524.431102935794</v>
-      </c>
       <c r="R9" t="n">
-        <v>17.01987577613088</v>
+        <v>531.21</v>
       </c>
       <c r="S9" t="n">
-        <v>524.2451854116678</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>16.86006025099044</v>
+        <v>522.52</v>
       </c>
       <c r="U9" t="n">
-        <v>520.7536934877667</v>
+        <v>15.73</v>
       </c>
       <c r="V9" t="n">
-        <v>20.33605312548383</v>
+        <v>520.66</v>
       </c>
       <c r="W9" t="n">
-        <v>521.355686491927</v>
+        <v>14.83</v>
       </c>
       <c r="X9" t="n">
-        <v>22.03675837641385</v>
+        <v>521.83</v>
       </c>
       <c r="Y9" t="n">
-        <v>521.0938039024078</v>
+        <v>17.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.89901247220249</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>17.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>524.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>16.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>520.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>20.34</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>521.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>22.04</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>521.09</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>505.65</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>509.1666666666667</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>510.8375</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>511.99</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>513.4333333333333</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>514.7</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>515.425</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>515.9111111111112</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>516.115</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>68.62672584350793</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>57.53583424460119</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>51.0162826335867</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>46.90277070707017</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>44.21099662100168</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>42.44689118685338</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>40.76526554555974</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>40.0825937407705</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>39.51432366876599</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>325</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>325</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>325</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>325</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>325</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>325</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>325</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>325</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>325</v>
       </c>
-      <c r="BK9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>669</v>
-      </c>
       <c r="BT9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.5357142857142857</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.6</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.625</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.07272727272727272</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.7017543859649122</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.75</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>521.09</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>22.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S10_G7_518_20_REL2</t>
+          <t>S09_G7_518_18_REL2</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>518</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>26.68643439584878</v>
       </c>
       <c r="D10" t="n">
-        <v>29.65159377316531</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
         <v>518</v>
@@ -2820,244 +3139,277 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>522.4644362378677</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16.20536188252549</v>
-      </c>
-      <c r="K10" t="n">
-        <v>532.0326091985551</v>
-      </c>
-      <c r="L10" t="n">
-        <v>15.83156336063616</v>
-      </c>
-      <c r="M10" t="n">
-        <v>524.4127787773309</v>
-      </c>
-      <c r="N10" t="n">
-        <v>26.70183230512124</v>
-      </c>
-      <c r="O10" t="n">
-        <v>522.2567581249104</v>
-      </c>
-      <c r="P10" t="n">
-        <v>25.38728515930306</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>521.8070452096002</v>
-      </c>
       <c r="R10" t="n">
-        <v>26.90654963860891</v>
+        <v>533.8</v>
       </c>
       <c r="S10" t="n">
-        <v>521.5937290009193</v>
+        <v>3.31</v>
       </c>
       <c r="T10" t="n">
-        <v>26.62095932809449</v>
+        <v>530.37</v>
       </c>
       <c r="U10" t="n">
-        <v>521.4876599832056</v>
+        <v>18.02</v>
       </c>
       <c r="V10" t="n">
-        <v>24.96656594737268</v>
+        <v>531.22</v>
       </c>
       <c r="W10" t="n">
-        <v>520.8708076918631</v>
+        <v>15.58</v>
       </c>
       <c r="X10" t="n">
-        <v>24.57062526255782</v>
+        <v>525.16</v>
       </c>
       <c r="Y10" t="n">
-        <v>520.4381580911469</v>
+        <v>20.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>25.8624295156777</v>
+        <v>524.6799999999999</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>21.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>523.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>23.11</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>24.76</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>524.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>23.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>523.4299999999999</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>23.38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>505.45</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>510.1</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>513.3</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>514.78</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>515.6416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>516.2785714285715</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>516.79375</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>516.7833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>516.8150000000001</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>70.46273837994093</v>
+        <v>504.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>60.26792955903939</v>
+        <v>510.5833333333333</v>
       </c>
       <c r="AU10" t="n">
-        <v>54.37793670230602</v>
+        <v>513.9125</v>
       </c>
       <c r="AV10" t="n">
-        <v>50.61888580362076</v>
+        <v>515.38</v>
       </c>
       <c r="AW10" t="n">
-        <v>47.60651143021882</v>
+        <v>516.6583333333333</v>
       </c>
       <c r="AX10" t="n">
-        <v>45.4537548122332</v>
+        <v>516.9357142857143</v>
       </c>
       <c r="AY10" t="n">
-        <v>43.60749604067517</v>
+        <v>517.06875</v>
       </c>
       <c r="AZ10" t="n">
-        <v>41.97423482195821</v>
+        <v>517.1833333333333</v>
       </c>
       <c r="BA10" t="n">
-        <v>40.77193612032669</v>
+        <v>516.84</v>
       </c>
       <c r="BB10" t="n">
-        <v>324</v>
+        <v>68.88330712153707</v>
       </c>
       <c r="BC10" t="n">
-        <v>324</v>
+        <v>59.68592566277433</v>
       </c>
       <c r="BD10" t="n">
-        <v>324</v>
+        <v>54.09117158788484</v>
       </c>
       <c r="BE10" t="n">
-        <v>324</v>
+        <v>49.97655050121006</v>
       </c>
       <c r="BF10" t="n">
-        <v>324</v>
+        <v>47.08954162609311</v>
       </c>
       <c r="BG10" t="n">
-        <v>324</v>
+        <v>44.90374001513614</v>
       </c>
       <c r="BH10" t="n">
-        <v>324</v>
+        <v>43.76744250510304</v>
       </c>
       <c r="BI10" t="n">
-        <v>324</v>
+        <v>42.5436344631407</v>
       </c>
       <c r="BJ10" t="n">
-        <v>324</v>
+        <v>40.92681761388246</v>
       </c>
       <c r="BK10" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BL10" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BM10" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BN10" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BO10" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BP10" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BQ10" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BR10" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BS10" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.6</v>
+        <v>669</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.8125</v>
+        <v>669</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.9473684210526315</v>
+        <v>669</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.9583333333333334</v>
+        <v>669</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.9666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.918918918918919</v>
+        <v>669</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.9534883720930233</v>
+        <v>669</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.9803921568627451</v>
+        <v>669</v>
       </c>
       <c r="CB10" t="n">
-        <v>1</v>
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>523.4299999999999</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>23.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S09_G7_518_18_REL2</t>
+          <t>S10_G7_518_20_REL2</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>518</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D11" t="n">
-        <v>26.68643439584878</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
         <v>518</v>
@@ -3066,720 +3418,819 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>533.8009128597561</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.311288120989897</v>
-      </c>
-      <c r="K11" t="n">
-        <v>530.3696327162593</v>
-      </c>
-      <c r="L11" t="n">
-        <v>18.01791133461547</v>
-      </c>
-      <c r="M11" t="n">
-        <v>531.2164342323892</v>
-      </c>
-      <c r="N11" t="n">
-        <v>15.57646985748805</v>
-      </c>
-      <c r="O11" t="n">
-        <v>525.160304937495</v>
-      </c>
-      <c r="P11" t="n">
-        <v>20.58756733508421</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>524.6773115340391</v>
-      </c>
       <c r="R11" t="n">
-        <v>21.46227801597302</v>
+        <v>522.46</v>
       </c>
       <c r="S11" t="n">
-        <v>523.749207579903</v>
+        <v>16.21</v>
       </c>
       <c r="T11" t="n">
-        <v>23.10726158886641</v>
+        <v>532.03</v>
       </c>
       <c r="U11" t="n">
-        <v>524.0004262961368</v>
+        <v>15.83</v>
       </c>
       <c r="V11" t="n">
-        <v>24.7602880988227</v>
+        <v>524.41</v>
       </c>
       <c r="W11" t="n">
-        <v>524.1568241256115</v>
+        <v>26.7</v>
       </c>
       <c r="X11" t="n">
-        <v>23.19383697983062</v>
+        <v>522.26</v>
       </c>
       <c r="Y11" t="n">
-        <v>523.429783212379</v>
+        <v>25.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.37508565436526</v>
+        <v>521.8099999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>26.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>521.59</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>26.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>521.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>24.97</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>520.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>24.57</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>520.4400000000001</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>25.86</v>
       </c>
       <c r="AJ11" t="n">
-        <v>504.8</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>510.5833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>513.9125</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>515.38</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>516.6583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>516.9357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>517.06875</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>517.1833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>516.84</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>68.88330712153707</v>
+        <v>505.45</v>
       </c>
       <c r="AT11" t="n">
-        <v>59.68592566277433</v>
+        <v>510.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>54.09117158788484</v>
+        <v>513.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>49.97655050121006</v>
+        <v>514.78</v>
       </c>
       <c r="AW11" t="n">
-        <v>47.08954162609311</v>
+        <v>515.6416666666667</v>
       </c>
       <c r="AX11" t="n">
-        <v>44.90374001513614</v>
+        <v>516.2785714285715</v>
       </c>
       <c r="AY11" t="n">
-        <v>43.76744250510304</v>
+        <v>516.79375</v>
       </c>
       <c r="AZ11" t="n">
-        <v>42.5436344631407</v>
+        <v>516.7833333333333</v>
       </c>
       <c r="BA11" t="n">
-        <v>40.92681761388246</v>
+        <v>516.8150000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>322</v>
+        <v>70.46273837994093</v>
       </c>
       <c r="BC11" t="n">
-        <v>322</v>
+        <v>60.26792955903939</v>
       </c>
       <c r="BD11" t="n">
-        <v>322</v>
+        <v>54.37793670230602</v>
       </c>
       <c r="BE11" t="n">
-        <v>322</v>
+        <v>50.61888580362076</v>
       </c>
       <c r="BF11" t="n">
-        <v>322</v>
+        <v>47.60651143021882</v>
       </c>
       <c r="BG11" t="n">
-        <v>322</v>
+        <v>45.4537548122332</v>
       </c>
       <c r="BH11" t="n">
-        <v>322</v>
+        <v>43.60749604067517</v>
       </c>
       <c r="BI11" t="n">
-        <v>322</v>
+        <v>41.97423482195821</v>
       </c>
       <c r="BJ11" t="n">
-        <v>322</v>
+        <v>40.77193612032669</v>
       </c>
       <c r="BK11" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BL11" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BM11" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BN11" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BO11" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BP11" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BQ11" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BR11" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BS11" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.125</v>
+        <v>669</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.7931034482758621</v>
+        <v>669</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.05714285714285714</v>
+        <v>669</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.9285714285714286</v>
+        <v>669</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.8653846153846154</v>
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.918918918918919</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.9534883720930233</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.9803921568627451</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>520.4400000000001</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>25.86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S12_G7_522_18_REL2</t>
+          <t>S11_G7_518_18_REL2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C12" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D12" t="n">
         <v>18</v>
       </c>
-      <c r="D12" t="n">
-        <v>26.68643439584878</v>
-      </c>
       <c r="E12" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F12" t="n">
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>542.9999999999944</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.0644567372889345</v>
-      </c>
-      <c r="K12" t="n">
-        <v>521.3474556226213</v>
-      </c>
-      <c r="L12" t="n">
-        <v>17.00826909082814</v>
-      </c>
-      <c r="M12" t="n">
-        <v>519.2534950341557</v>
-      </c>
-      <c r="N12" t="n">
-        <v>18.43485724144813</v>
-      </c>
-      <c r="O12" t="n">
-        <v>520.3705448674518</v>
-      </c>
-      <c r="P12" t="n">
-        <v>17.69093690325814</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>521.5577499048092</v>
-      </c>
       <c r="R12" t="n">
-        <v>17.72680953792904</v>
+        <v>516.84</v>
       </c>
       <c r="S12" t="n">
-        <v>523.4501781014693</v>
+        <v>8.51</v>
       </c>
       <c r="T12" t="n">
-        <v>17.99933486941813</v>
+        <v>523.2</v>
       </c>
       <c r="U12" t="n">
-        <v>523.3218443317171</v>
+        <v>16.03</v>
       </c>
       <c r="V12" t="n">
-        <v>17.79986403233429</v>
+        <v>516.58</v>
       </c>
       <c r="W12" t="n">
-        <v>523.5261300422859</v>
+        <v>17.57</v>
       </c>
       <c r="X12" t="n">
-        <v>16.8410425154048</v>
+        <v>513.64</v>
       </c>
       <c r="Y12" t="n">
-        <v>522.9840284710701</v>
+        <v>19.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>16.55206917396063</v>
+        <v>514.97</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>19.49</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>513.6900000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>20.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>23.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>514.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>23.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>515.59</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>23.42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>506.5</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>509.95</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>511.3875</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>512.71</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>513.225</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>513.9642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>514.2875</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>514.7166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>514.745</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>71.32566158122896</v>
+        <v>500.325</v>
       </c>
       <c r="AT12" t="n">
-        <v>60.41176072035423</v>
+        <v>506.8666666666667</v>
       </c>
       <c r="AU12" t="n">
-        <v>53.79068082623606</v>
+        <v>509.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>49.08977388418081</v>
+        <v>509.15</v>
       </c>
       <c r="AW12" t="n">
-        <v>45.741932348776</v>
+        <v>509.25</v>
       </c>
       <c r="AX12" t="n">
-        <v>43.09962060063136</v>
+        <v>509.6285714285714</v>
       </c>
       <c r="AY12" t="n">
-        <v>41.2394513027271</v>
+        <v>510.40625</v>
       </c>
       <c r="AZ12" t="n">
-        <v>39.83372036074182</v>
+        <v>511.1833333333333</v>
       </c>
       <c r="BA12" t="n">
-        <v>38.25022843069045</v>
+        <v>511.58</v>
       </c>
       <c r="BB12" t="n">
-        <v>328</v>
+        <v>68.39970303298107</v>
       </c>
       <c r="BC12" t="n">
-        <v>328</v>
+        <v>58.48688361979595</v>
       </c>
       <c r="BD12" t="n">
-        <v>328</v>
+        <v>52.51485504121667</v>
       </c>
       <c r="BE12" t="n">
-        <v>328</v>
+        <v>48.18410007460967</v>
       </c>
       <c r="BF12" t="n">
-        <v>328</v>
+        <v>45.10436970701028</v>
       </c>
       <c r="BG12" t="n">
-        <v>328</v>
+        <v>42.7882398491426</v>
       </c>
       <c r="BH12" t="n">
-        <v>328</v>
+        <v>42.10898016976308</v>
       </c>
       <c r="BI12" t="n">
-        <v>328</v>
+        <v>42.34323703051318</v>
       </c>
       <c r="BJ12" t="n">
-        <v>328</v>
+        <v>41.75180954162346</v>
       </c>
       <c r="BK12" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BL12" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BM12" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BN12" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BO12" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BP12" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BQ12" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BR12" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BS12" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.4761904761904762</v>
+        <v>669</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.4838709677419355</v>
+        <v>669</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.4390243902439024</v>
+        <v>669</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.4313725490196079</v>
+        <v>669</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.4262295081967213</v>
+        <v>669</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.4507042253521127</v>
+        <v>669</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.4814814814814815</v>
+        <v>669</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.5</v>
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.7837837837837838</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.9807692307692307</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>515.59</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>23.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S11_G7_518_18_REL2</t>
+          <t>S12_G7_522_18_REL2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C13" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D13" t="n">
         <v>18</v>
       </c>
-      <c r="D13" t="n">
-        <v>26.68643439584878</v>
-      </c>
       <c r="E13" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F13" t="n">
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>85.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>516.8364001734135</v>
-      </c>
-      <c r="J13" t="n">
-        <v>8.505889911060009</v>
-      </c>
-      <c r="K13" t="n">
-        <v>523.2034084839422</v>
-      </c>
-      <c r="L13" t="n">
-        <v>16.029000363225</v>
-      </c>
-      <c r="M13" t="n">
-        <v>516.58096351591</v>
-      </c>
-      <c r="N13" t="n">
-        <v>17.56718682201198</v>
-      </c>
-      <c r="O13" t="n">
-        <v>513.6389150287152</v>
-      </c>
-      <c r="P13" t="n">
-        <v>19.39527978949494</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>514.974709368846</v>
-      </c>
       <c r="R13" t="n">
-        <v>19.48839452278236</v>
+        <v>543</v>
       </c>
       <c r="S13" t="n">
-        <v>513.689868302767</v>
+        <v>0.06</v>
       </c>
       <c r="T13" t="n">
-        <v>20.72643098241717</v>
+        <v>521.35</v>
       </c>
       <c r="U13" t="n">
-        <v>514.6831814815147</v>
+        <v>17.01</v>
       </c>
       <c r="V13" t="n">
-        <v>23.02384179200671</v>
+        <v>519.25</v>
       </c>
       <c r="W13" t="n">
-        <v>514.8922975727403</v>
+        <v>18.43</v>
       </c>
       <c r="X13" t="n">
-        <v>23.3533924002244</v>
+        <v>520.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>515.588740032051</v>
+        <v>17.69</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.42068195629523</v>
+        <v>521.5599999999999</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>17.73</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>523.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>523.3200000000001</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>523.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>16.84</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>522.98</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>16.55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>500.325</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>506.8666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>509.2</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>509.15</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>509.25</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>509.6285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>510.40625</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>511.1833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>511.58</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>68.39970303298107</v>
+        <v>506.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>58.48688361979595</v>
+        <v>509.95</v>
       </c>
       <c r="AU13" t="n">
-        <v>52.51485504121667</v>
+        <v>511.3875</v>
       </c>
       <c r="AV13" t="n">
-        <v>48.18410007460967</v>
+        <v>512.71</v>
       </c>
       <c r="AW13" t="n">
-        <v>45.10436970701028</v>
+        <v>513.225</v>
       </c>
       <c r="AX13" t="n">
-        <v>42.7882398491426</v>
+        <v>513.9642857142857</v>
       </c>
       <c r="AY13" t="n">
-        <v>42.10898016976308</v>
+        <v>514.2875</v>
       </c>
       <c r="AZ13" t="n">
-        <v>42.34323703051318</v>
+        <v>514.7166666666667</v>
       </c>
       <c r="BA13" t="n">
-        <v>41.75180954162346</v>
+        <v>514.745</v>
       </c>
       <c r="BB13" t="n">
-        <v>322</v>
+        <v>71.32566158122896</v>
       </c>
       <c r="BC13" t="n">
-        <v>322</v>
+        <v>60.41176072035423</v>
       </c>
       <c r="BD13" t="n">
-        <v>322</v>
+        <v>53.79068082623606</v>
       </c>
       <c r="BE13" t="n">
-        <v>322</v>
+        <v>49.08977388418081</v>
       </c>
       <c r="BF13" t="n">
-        <v>322</v>
+        <v>45.741932348776</v>
       </c>
       <c r="BG13" t="n">
-        <v>322</v>
+        <v>43.09962060063136</v>
       </c>
       <c r="BH13" t="n">
-        <v>322</v>
+        <v>41.2394513027271</v>
       </c>
       <c r="BI13" t="n">
-        <v>322</v>
+        <v>39.83372036074182</v>
       </c>
       <c r="BJ13" t="n">
-        <v>322</v>
+        <v>38.25022843069045</v>
       </c>
       <c r="BK13" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
       <c r="BL13" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
       <c r="BM13" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
       <c r="BN13" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
       <c r="BO13" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
       <c r="BP13" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
       <c r="BQ13" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
       <c r="BR13" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
       <c r="BS13" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.6153846153846154</v>
+        <v>669</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.09523809523809523</v>
+        <v>669</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.7837837837837838</v>
+        <v>669</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.7872340425531915</v>
+        <v>669</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.86</v>
+        <v>669</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.92</v>
+        <v>669</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.9807692307692307</v>
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.4390243902439024</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.4313725490196079</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.4262295081967213</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.4507042253521127</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>522.98</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>16.55</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>521</v>
       </c>
       <c r="C14" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D14" t="n">
         <v>22</v>
-      </c>
-      <c r="D14" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E14" t="n">
         <v>521</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>512.7953198714239</v>
-      </c>
-      <c r="J14" t="n">
-        <v>30.57685677754137</v>
-      </c>
-      <c r="K14" t="n">
-        <v>519.3867777809361</v>
-      </c>
-      <c r="L14" t="n">
-        <v>34.63441950834644</v>
-      </c>
-      <c r="M14" t="n">
-        <v>519.646472577935</v>
-      </c>
-      <c r="N14" t="n">
-        <v>30.45431763371801</v>
-      </c>
-      <c r="O14" t="n">
-        <v>518.0965754154183</v>
-      </c>
-      <c r="P14" t="n">
-        <v>31.53369017781477</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>519.460905741823</v>
-      </c>
       <c r="R14" t="n">
-        <v>30.15133616202127</v>
+        <v>512.8</v>
       </c>
       <c r="S14" t="n">
-        <v>519.5898661898181</v>
+        <v>30.58</v>
       </c>
       <c r="T14" t="n">
-        <v>30.09529048434551</v>
+        <v>519.39</v>
       </c>
       <c r="U14" t="n">
-        <v>520.349748671281</v>
+        <v>34.63</v>
       </c>
       <c r="V14" t="n">
-        <v>29.07244122495235</v>
+        <v>519.65</v>
       </c>
       <c r="W14" t="n">
-        <v>520.0174617646578</v>
+        <v>30.45</v>
       </c>
       <c r="X14" t="n">
-        <v>29.2093816503974</v>
+        <v>518.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>520.948266110329</v>
+        <v>31.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>29.61121120194667</v>
+        <v>519.46</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>30.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>519.59</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>30.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>520.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>29.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>520.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>520.95</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>29.61</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>511.175</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>514.2666666666667</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>515.65</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>516.63</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>515.7916666666666</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>515.65</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>516.01875</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>515.0833333333334</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>514.855</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>71.51184779461373</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>62.76141773060544</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>57.47501631143744</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>53.36303121075489</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>49.95629687258877</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>48.0798331646737</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>46.67580635015854</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>46.50792943144212</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>46.06391185081875</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>340</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>340</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>340</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>340</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>340</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>340</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>340</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>340</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>340</v>
       </c>
-      <c r="BK14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>669</v>
-      </c>
       <c r="BT14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.9629629629629629</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.7428571428571429</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.6829268292682927</v>
       </c>
-      <c r="CA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB14" t="n">
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
         <v>0.7708333333333334</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>520.95</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>29.61</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>518</v>
       </c>
       <c r="C15" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D15" t="n">
         <v>22</v>
-      </c>
-      <c r="D15" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E15" t="n">
         <v>518</v>
@@ -4050,720 +4534,819 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>525.6005839242963</v>
-      </c>
-      <c r="J15" t="n">
-        <v>22.97564189252287</v>
-      </c>
-      <c r="K15" t="n">
-        <v>512.1773452149864</v>
-      </c>
-      <c r="L15" t="n">
-        <v>23.50050729813895</v>
-      </c>
-      <c r="M15" t="n">
-        <v>514.5281048306929</v>
-      </c>
-      <c r="N15" t="n">
-        <v>21.43715641425972</v>
-      </c>
-      <c r="O15" t="n">
-        <v>513.4721645647792</v>
-      </c>
-      <c r="P15" t="n">
-        <v>23.75659301563698</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>516.3224465477939</v>
-      </c>
       <c r="R15" t="n">
-        <v>21.79769019274597</v>
+        <v>525.6</v>
       </c>
       <c r="S15" t="n">
-        <v>516.6693485084821</v>
+        <v>22.98</v>
       </c>
       <c r="T15" t="n">
-        <v>22.63150180593268</v>
+        <v>512.1799999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>518.9610294459063</v>
+        <v>23.5</v>
       </c>
       <c r="V15" t="n">
-        <v>23.69547960789269</v>
+        <v>514.53</v>
       </c>
       <c r="W15" t="n">
-        <v>519.2482726842647</v>
+        <v>21.44</v>
       </c>
       <c r="X15" t="n">
-        <v>23.26230781134802</v>
+        <v>513.47</v>
       </c>
       <c r="Y15" t="n">
-        <v>519.2699317811727</v>
+        <v>23.76</v>
       </c>
       <c r="Z15" t="n">
-        <v>23.09623998816217</v>
+        <v>516.3200000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>516.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>22.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>518.96</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>519.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>23.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>519.27</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>508.775</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>512.2833333333333</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>512.4875</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>513.1</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>513.6583333333333</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>513.5</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>513.8625</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>514.7277777777778</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>515.1900000000001</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>67.19355902912123</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>57.12065932937243</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>51.08840224307274</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>46.79668791698831</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>43.76214037904859</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>41.73273809099312</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>40.21978485459612</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>40.07296547210345</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>39.88463237890002</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>344</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>344</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>344</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>344</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>344</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>344</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>344</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>344</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>344</v>
       </c>
-      <c r="BK15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>669</v>
-      </c>
       <c r="BT15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.9</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>1</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.04545454545454546</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>519.27</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>23.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S16_G7_521_21_REL2</t>
+          <t>S15_G7_520_21_REL2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C16" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D16" t="n">
         <v>21</v>
       </c>
-      <c r="D16" t="n">
-        <v>31.13417346182357</v>
-      </c>
       <c r="E16" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F16" t="n">
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>520.9960490895161</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17.69466520895056</v>
-      </c>
-      <c r="K16" t="n">
-        <v>527.7442129453668</v>
-      </c>
-      <c r="L16" t="n">
-        <v>14.91020976168843</v>
-      </c>
-      <c r="M16" t="n">
-        <v>528.542190804904</v>
-      </c>
-      <c r="N16" t="n">
-        <v>17.68893813832543</v>
-      </c>
-      <c r="O16" t="n">
-        <v>524.4769918090406</v>
-      </c>
-      <c r="P16" t="n">
-        <v>23.35447302083024</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>524.6438264963889</v>
-      </c>
       <c r="R16" t="n">
-        <v>22.65231685870885</v>
+        <v>529.1</v>
       </c>
       <c r="S16" t="n">
-        <v>525.1947987431669</v>
+        <v>20.69</v>
       </c>
       <c r="T16" t="n">
-        <v>22.45049653275351</v>
+        <v>528.4</v>
       </c>
       <c r="U16" t="n">
-        <v>524.3698305683878</v>
+        <v>25.29</v>
       </c>
       <c r="V16" t="n">
-        <v>22.27933172320143</v>
+        <v>520.79</v>
       </c>
       <c r="W16" t="n">
-        <v>527.0297413897323</v>
+        <v>24.59</v>
       </c>
       <c r="X16" t="n">
-        <v>22.13789741195692</v>
+        <v>522.98</v>
       </c>
       <c r="Y16" t="n">
-        <v>525.483644354988</v>
+        <v>22.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.06794017392779</v>
+        <v>519.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>21.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>518.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>21.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>517.97</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>21.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>517.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>21.68</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>21.22</v>
       </c>
       <c r="AJ16" t="n">
-        <v>508.45</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>511.0666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>513.3875</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>514.58</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>515.2833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>517.2142857142857</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>517.59375</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>518.0055555555556</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>518.075</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>72.3539736296494</v>
+        <v>512.675</v>
       </c>
       <c r="AT16" t="n">
-        <v>60.87031752468157</v>
+        <v>515.3166666666667</v>
       </c>
       <c r="AU16" t="n">
-        <v>54.59590042988576</v>
+        <v>515.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>50.42681429557096</v>
+        <v>515.85</v>
       </c>
       <c r="AW16" t="n">
-        <v>47.68074092917973</v>
+        <v>514.9666666666667</v>
       </c>
       <c r="AX16" t="n">
-        <v>46.233071915843</v>
+        <v>514.4642857142857</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.24707573317699</v>
+        <v>514.275</v>
       </c>
       <c r="AZ16" t="n">
-        <v>42.85498768096664</v>
+        <v>513.1777777777778</v>
       </c>
       <c r="BA16" t="n">
-        <v>41.5642800370703</v>
+        <v>512.745</v>
       </c>
       <c r="BB16" t="n">
-        <v>322</v>
+        <v>72.75279633801027</v>
       </c>
       <c r="BC16" t="n">
-        <v>322</v>
+        <v>62.68293007049225</v>
       </c>
       <c r="BD16" t="n">
-        <v>322</v>
+        <v>56.84087437751111</v>
       </c>
       <c r="BE16" t="n">
-        <v>322</v>
+        <v>52.2716701474135</v>
       </c>
       <c r="BF16" t="n">
-        <v>322</v>
+        <v>48.38455906129099</v>
       </c>
       <c r="BG16" t="n">
-        <v>322</v>
+        <v>45.88812649325775</v>
       </c>
       <c r="BH16" t="n">
-        <v>322</v>
+        <v>43.96617307658241</v>
       </c>
       <c r="BI16" t="n">
-        <v>322</v>
+        <v>42.89550035396818</v>
       </c>
       <c r="BJ16" t="n">
-        <v>322</v>
+        <v>41.60120160524212</v>
       </c>
       <c r="BK16" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BL16" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BM16" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BN16" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BO16" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BP16" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BQ16" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BR16" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BS16" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BT16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
         <v>1</v>
       </c>
-      <c r="BU16" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>0.8709677419354839</v>
-      </c>
-      <c r="BY16" t="n">
+      <c r="CD16" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CE16" t="n">
         <v>1</v>
       </c>
-      <c r="BZ16" t="n">
-        <v>0.9722222222222222</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0.975609756097561</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>0.9787234042553191</v>
+      <c r="CF16" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.5869565217391305</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.723404255319149</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>515.8099999999999</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>21.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S15_G7_520_21_REL2</t>
+          <t>S16_G7_521_21_REL2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C17" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D17" t="n">
         <v>21</v>
       </c>
-      <c r="D17" t="n">
-        <v>31.13417346182357</v>
-      </c>
       <c r="E17" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>84.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>529.103796411678</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20.68643250443377</v>
-      </c>
-      <c r="K17" t="n">
-        <v>528.3961324557285</v>
-      </c>
-      <c r="L17" t="n">
-        <v>25.28785769279113</v>
-      </c>
-      <c r="M17" t="n">
-        <v>520.7931908649676</v>
-      </c>
-      <c r="N17" t="n">
-        <v>24.58993029382849</v>
-      </c>
-      <c r="O17" t="n">
-        <v>522.9773158276048</v>
-      </c>
-      <c r="P17" t="n">
-        <v>22.24828408907146</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>519.7307124464459</v>
-      </c>
       <c r="R17" t="n">
-        <v>21.8396014671637</v>
+        <v>521</v>
       </c>
       <c r="S17" t="n">
-        <v>518.7224008441087</v>
+        <v>17.69</v>
       </c>
       <c r="T17" t="n">
-        <v>21.83865027711025</v>
+        <v>527.74</v>
       </c>
       <c r="U17" t="n">
-        <v>517.9696208569819</v>
+        <v>14.91</v>
       </c>
       <c r="V17" t="n">
-        <v>21.17654338478488</v>
+        <v>528.54</v>
       </c>
       <c r="W17" t="n">
-        <v>517.0463599721229</v>
+        <v>17.69</v>
       </c>
       <c r="X17" t="n">
-        <v>21.68327513747584</v>
+        <v>524.48</v>
       </c>
       <c r="Y17" t="n">
-        <v>515.8095346522736</v>
+        <v>23.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.2236662032212</v>
+        <v>524.64</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>22.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>525.1900000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>22.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>524.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>22.28</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>527.03</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>22.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>525.48</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>21.07</v>
       </c>
       <c r="AJ17" t="n">
-        <v>512.675</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>515.3166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>515.8</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>515.85</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>514.9666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>514.4642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>514.275</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>513.1777777777778</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>512.745</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>72.75279633801027</v>
+        <v>508.45</v>
       </c>
       <c r="AT17" t="n">
-        <v>62.68293007049225</v>
+        <v>511.0666666666667</v>
       </c>
       <c r="AU17" t="n">
-        <v>56.84087437751111</v>
+        <v>513.3875</v>
       </c>
       <c r="AV17" t="n">
-        <v>52.2716701474135</v>
+        <v>514.58</v>
       </c>
       <c r="AW17" t="n">
-        <v>48.38455906129099</v>
+        <v>515.2833333333333</v>
       </c>
       <c r="AX17" t="n">
-        <v>45.88812649325775</v>
+        <v>517.2142857142857</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.96617307658241</v>
+        <v>517.59375</v>
       </c>
       <c r="AZ17" t="n">
-        <v>42.89550035396818</v>
+        <v>518.0055555555556</v>
       </c>
       <c r="BA17" t="n">
-        <v>41.60120160524212</v>
+        <v>518.075</v>
       </c>
       <c r="BB17" t="n">
-        <v>335</v>
+        <v>72.3539736296494</v>
       </c>
       <c r="BC17" t="n">
-        <v>335</v>
+        <v>60.87031752468157</v>
       </c>
       <c r="BD17" t="n">
-        <v>335</v>
+        <v>54.59590042988576</v>
       </c>
       <c r="BE17" t="n">
-        <v>335</v>
+        <v>50.42681429557096</v>
       </c>
       <c r="BF17" t="n">
-        <v>335</v>
+        <v>47.68074092917973</v>
       </c>
       <c r="BG17" t="n">
-        <v>335</v>
+        <v>46.233071915843</v>
       </c>
       <c r="BH17" t="n">
-        <v>335</v>
+        <v>44.24707573317699</v>
       </c>
       <c r="BI17" t="n">
-        <v>335</v>
+        <v>42.85498768096664</v>
       </c>
       <c r="BJ17" t="n">
-        <v>335</v>
+        <v>41.5642800370703</v>
       </c>
       <c r="BK17" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BL17" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BM17" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BN17" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BO17" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BP17" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BQ17" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BR17" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BS17" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BT17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
         <v>1</v>
       </c>
-      <c r="BU17" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="BV17" t="n">
+      <c r="CD17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="CH17" t="n">
         <v>1</v>
       </c>
-      <c r="BW17" t="n">
-        <v>0.9259259259259259</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0.5869565217391305</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0.723404255319149</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>0.7735849056603774</v>
+      <c r="CI17" t="n">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.975609756097561</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.9787234042553191</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>525.48</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>21.07</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>521</v>
       </c>
       <c r="C18" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D18" t="n">
         <v>18</v>
-      </c>
-      <c r="D18" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E18" t="n">
         <v>521</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>527.4984425264707</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20.15729798854712</v>
-      </c>
-      <c r="K18" t="n">
-        <v>522.8756293841366</v>
-      </c>
-      <c r="L18" t="n">
-        <v>18.68182387512339</v>
-      </c>
-      <c r="M18" t="n">
-        <v>524.813293663718</v>
-      </c>
-      <c r="N18" t="n">
-        <v>19.52949850600917</v>
-      </c>
-      <c r="O18" t="n">
-        <v>526.5666303633631</v>
-      </c>
-      <c r="P18" t="n">
-        <v>18.10362615981406</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>526.3309830976599</v>
-      </c>
       <c r="R18" t="n">
-        <v>18.4135552498674</v>
+        <v>527.5</v>
       </c>
       <c r="S18" t="n">
-        <v>523.8534526691468</v>
+        <v>20.16</v>
       </c>
       <c r="T18" t="n">
-        <v>20.66505319723042</v>
+        <v>522.88</v>
       </c>
       <c r="U18" t="n">
-        <v>523.0705385951753</v>
+        <v>18.68</v>
       </c>
       <c r="V18" t="n">
-        <v>20.64182214527554</v>
+        <v>524.8099999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>522.5505342018483</v>
+        <v>19.53</v>
       </c>
       <c r="X18" t="n">
-        <v>21.10989475759313</v>
+        <v>526.5700000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>523.2546469385533</v>
+        <v>18.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.13183934660279</v>
+        <v>526.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>18.41</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>523.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>20.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>523.0700000000001</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>20.64</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>522.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>21.11</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>523.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>21.13</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>510.425</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>512.3</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>513.4</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>514.23</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>515.1166666666667</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>515.0285714285715</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>515.54375</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>515.4388888888889</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>515.6</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>72.82372123834375</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>62.16652368169436</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>55.48909802835148</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>51.27218641719895</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>48.04116001467445</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>45.35210545705409</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>43.21354632447446</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>41.53702015323049</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>40.31240503864784</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>326</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>326</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>326</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>326</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>326</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>326</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>326</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>326</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>326</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
         <v>1</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.8717948717948718</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.7959183673469388</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.7543859649122807</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.78125</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.75</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>523.25</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>21.13</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>519</v>
       </c>
       <c r="C19" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D19" t="n">
         <v>22</v>
-      </c>
-      <c r="D19" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E19" t="n">
         <v>519</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>538.2826705689716</v>
-      </c>
-      <c r="J19" t="n">
-        <v>25.46856458119242</v>
-      </c>
-      <c r="K19" t="n">
-        <v>526.8013739404539</v>
-      </c>
-      <c r="L19" t="n">
-        <v>27.42728584898739</v>
-      </c>
-      <c r="M19" t="n">
-        <v>522.3377950884853</v>
-      </c>
-      <c r="N19" t="n">
-        <v>29.24549700288712</v>
-      </c>
-      <c r="O19" t="n">
-        <v>519.0648171304676</v>
-      </c>
-      <c r="P19" t="n">
-        <v>26.97391491065317</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>518.9531419082957</v>
-      </c>
       <c r="R19" t="n">
-        <v>26.44886424727021</v>
+        <v>538.28</v>
       </c>
       <c r="S19" t="n">
-        <v>520.5288772727116</v>
+        <v>25.47</v>
       </c>
       <c r="T19" t="n">
-        <v>30.6555462304668</v>
+        <v>526.8</v>
       </c>
       <c r="U19" t="n">
-        <v>521.1965096665328</v>
+        <v>27.43</v>
       </c>
       <c r="V19" t="n">
-        <v>31.31352305263936</v>
+        <v>522.34</v>
       </c>
       <c r="W19" t="n">
-        <v>520.5150221664176</v>
+        <v>29.25</v>
       </c>
       <c r="X19" t="n">
-        <v>31.00609090377365</v>
+        <v>519.0599999999999</v>
       </c>
       <c r="Y19" t="n">
-        <v>519.7198112070868</v>
+        <v>26.97</v>
       </c>
       <c r="Z19" t="n">
-        <v>29.53122363092136</v>
+        <v>518.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>26.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>520.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>30.66</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>521.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>31.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>520.52</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>31.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>519.72</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>29.53</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>520.65</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>520.75</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>520.625</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>519.83</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>518.6333333333333</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>517.8928571428571</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>517.85625</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>518.4722222222222</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>517.465</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>75.10810542145235</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>64.83353684629584</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>58.59551497341754</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>53.71127535257379</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>50.17119580883925</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>48.6630831664549</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>47.23939654501844</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>46.47609069374101</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>44.93482808468282</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>334</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>334</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>334</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>334</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>334</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>334</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>334</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>334</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>334</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.7058823529411765</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.7297297297297297</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.8</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.8478260869565217</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.7647058823529411</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>519.72</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>29.53</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>518</v>
       </c>
       <c r="C20" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D20" t="n">
         <v>19</v>
-      </c>
-      <c r="D20" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E20" t="n">
         <v>518</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>517.3136026967508</v>
-      </c>
-      <c r="J20" t="n">
-        <v>14.28219466923774</v>
-      </c>
-      <c r="K20" t="n">
-        <v>511.147806138516</v>
-      </c>
-      <c r="L20" t="n">
-        <v>21.72327681616125</v>
-      </c>
-      <c r="M20" t="n">
-        <v>509.8152885671864</v>
-      </c>
-      <c r="N20" t="n">
-        <v>22.54358054818369</v>
-      </c>
-      <c r="O20" t="n">
-        <v>512.2371447923031</v>
-      </c>
-      <c r="P20" t="n">
-        <v>21.33969964372921</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>512.7424104803479</v>
-      </c>
       <c r="R20" t="n">
-        <v>20.0794010545782</v>
+        <v>517.3099999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>512.8498656680888</v>
+        <v>14.28</v>
       </c>
       <c r="T20" t="n">
-        <v>18.82781967472377</v>
+        <v>511.15</v>
       </c>
       <c r="U20" t="n">
-        <v>513.4833627886336</v>
+        <v>21.72</v>
       </c>
       <c r="V20" t="n">
-        <v>19.5135058836422</v>
+        <v>509.82</v>
       </c>
       <c r="W20" t="n">
-        <v>513.0699627354207</v>
+        <v>22.54</v>
       </c>
       <c r="X20" t="n">
-        <v>18.6567090703891</v>
+        <v>512.24</v>
       </c>
       <c r="Y20" t="n">
-        <v>512.6361300139519</v>
+        <v>21.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.4402546579951</v>
+        <v>512.74</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>20.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>512.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>18.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>513.48</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>19.51</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>513.0700000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>18.66</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>512.64</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>18.44</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>503.55</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>506.05</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>507.475</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>508.81</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>509.7</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>510.0571428571429</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>510.31875</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>510.25</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>510.145</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>68.43133419713516</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>57.45880408315742</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>51.45847233449513</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>47.50109367161981</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>44.43583388812832</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>42.01577449152222</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>40.04706167045842</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>38.41843813703114</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>36.94947868373789</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>321</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>321</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>321</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>321</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>321</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>321</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>321</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>321</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>321</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.6129032258064516</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.6097560975609756</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.62</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.5666666666666667</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.7105263157894737</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>512.64</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>18.44</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>521</v>
       </c>
       <c r="C21" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D21" t="n">
         <v>18</v>
-      </c>
-      <c r="D21" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E21" t="n">
         <v>521</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>84.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>505.4409073675484</v>
-      </c>
-      <c r="J21" t="n">
-        <v>26.40622033506571</v>
-      </c>
-      <c r="K21" t="n">
-        <v>509.4123181166516</v>
-      </c>
-      <c r="L21" t="n">
-        <v>21.71484304048405</v>
-      </c>
-      <c r="M21" t="n">
-        <v>510.6991394950884</v>
-      </c>
-      <c r="N21" t="n">
-        <v>19.57533675169424</v>
-      </c>
-      <c r="O21" t="n">
-        <v>511.4755185237131</v>
-      </c>
-      <c r="P21" t="n">
-        <v>20.71418489340281</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>513.07248385808</v>
-      </c>
       <c r="R21" t="n">
-        <v>18.02159140921919</v>
+        <v>505.44</v>
       </c>
       <c r="S21" t="n">
-        <v>513.8222362179857</v>
+        <v>26.41</v>
       </c>
       <c r="T21" t="n">
-        <v>16.82539212707274</v>
+        <v>509.41</v>
       </c>
       <c r="U21" t="n">
-        <v>515.0282148316085</v>
+        <v>21.71</v>
       </c>
       <c r="V21" t="n">
-        <v>16.75200035355477</v>
+        <v>510.7</v>
       </c>
       <c r="W21" t="n">
-        <v>517.8496641145207</v>
+        <v>19.58</v>
       </c>
       <c r="X21" t="n">
-        <v>18.9898572158193</v>
+        <v>511.48</v>
       </c>
       <c r="Y21" t="n">
-        <v>519.0011493002746</v>
+        <v>20.71</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.96301672461642</v>
+        <v>513.0700000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>18.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>513.8200000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>16.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>515.03</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>517.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>18.99</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>18.96</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>490.775</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>497.4833333333333</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>501.0625</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>502.74</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>503.8333333333333</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>505.1071428571428</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>506.20625</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>508.2833333333334</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>510.6</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>75.1603244737541</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>62.99536799550336</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>55.66200314173035</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>50.65463848454552</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>46.91221115611111</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>43.97884173563651</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>41.84989499314783</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>41.23702152731747</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>41.66257313224904</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>318</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>318</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>318</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>318</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>318</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>318</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>318</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>318</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>318</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>0.375</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.4705882352941176</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.7407407407407407</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA21" t="n">
+      <c r="CI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ21" t="n">
         <v>0.9069767441860465</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>1</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>519</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>18.96</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>519.65</v>
       </c>
       <c r="C22" t="n">
+        <v>29.20681986656783</v>
+      </c>
+      <c r="D22" t="n">
         <v>19.7</v>
-      </c>
-      <c r="D22" t="n">
-        <v>29.20681986656783</v>
       </c>
       <c r="E22" t="n">
         <v>519.65</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4647500000000001</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>82.825</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.2145</v>
+      </c>
       <c r="I22" t="n">
-        <v>525.034984948017</v>
+        <v>2.157</v>
       </c>
       <c r="J22" t="n">
-        <v>17.54750867361738</v>
+        <v>2.1095</v>
       </c>
       <c r="K22" t="n">
-        <v>522.0934685791738</v>
+        <v>2.0615</v>
       </c>
       <c r="L22" t="n">
-        <v>20.60448021993871</v>
+        <v>2.036</v>
       </c>
       <c r="M22" t="n">
-        <v>520.1124834090326</v>
+        <v>2.0205</v>
       </c>
       <c r="N22" t="n">
-        <v>21.51922928466715</v>
+        <v>2.7685</v>
       </c>
       <c r="O22" t="n">
-        <v>519.0156489605348</v>
+        <v>2.51</v>
       </c>
       <c r="P22" t="n">
-        <v>21.94647745688879</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>519.9252204519353</v>
-      </c>
+        <v>2.3275</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>21.7992641597274</v>
+        <v>525.0350000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>519.8440302146705</v>
+        <v>17.548</v>
       </c>
       <c r="T22" t="n">
-        <v>22.76898285562653</v>
+        <v>522.0939999999998</v>
       </c>
       <c r="U22" t="n">
-        <v>519.995699178721</v>
+        <v>20.6045</v>
       </c>
       <c r="V22" t="n">
-        <v>23.09872561617766</v>
+        <v>520.1125</v>
       </c>
       <c r="W22" t="n">
-        <v>520.1216534927531</v>
+        <v>21.5195</v>
       </c>
       <c r="X22" t="n">
-        <v>22.88532341263952</v>
+        <v>519.0165</v>
       </c>
       <c r="Y22" t="n">
-        <v>520.0512925226353</v>
+        <v>21.9465</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.80021291377185</v>
+        <v>519.9245</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>21.799</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>519.8430000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>22.771</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>519.9955000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>23.0985</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>520.1224999999999</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>22.885</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>520.0509999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>22.8005</v>
       </c>
       <c r="AJ22" t="n">
-        <v>507.7362499999998</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>510.7583333333333</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>512.153125</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>507.7354999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>510.7594999999999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>512.1534999999999</v>
+      </c>
+      <c r="AV22" t="n">
         <v>512.7729999999999</v>
       </c>
-      <c r="AN22" t="n">
-        <v>513.2158333333334</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>513.6535714285712</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>514.1950000000001</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>514.4691666666668</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>514.6087500000001</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>71.00876474429353</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>60.63124363055065</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>54.41272239356498</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>50.06800805926549</v>
-      </c>
       <c r="AW22" t="n">
-        <v>46.98354385576262</v>
+        <v>513.216</v>
       </c>
       <c r="AX22" t="n">
-        <v>44.96252590043795</v>
+        <v>513.6535</v>
       </c>
       <c r="AY22" t="n">
-        <v>43.439506847193</v>
+        <v>514.1955</v>
       </c>
       <c r="AZ22" t="n">
-        <v>42.39521653545417</v>
+        <v>514.4690000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>41.35426527536565</v>
+        <v>514.611</v>
       </c>
       <c r="BB22" t="n">
+        <v>71.00749999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>60.63200000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>54.414</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>50.0675</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>46.98399999999999</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>44.9625</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>43.4405</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>42.3945</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>41.3525</v>
+      </c>
+      <c r="BK22" t="n">
         <v>330.15</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>330.15</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>330.15</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>330.15</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>330.15</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>330.15</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>330.15</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>330.15</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>330.15</v>
       </c>
-      <c r="BK22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>669</v>
-      </c>
       <c r="BT22" t="n">
-        <v>0.6866197691197692</v>
+        <v>669</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.6206600588953531</v>
+        <v>669</v>
       </c>
       <c r="BV22" t="n">
-        <v>0.7051773412352593</v>
+        <v>669</v>
       </c>
       <c r="BW22" t="n">
-        <v>0.7730746597130094</v>
+        <v>669</v>
       </c>
       <c r="BX22" t="n">
-        <v>0.7748499705676494</v>
+        <v>669</v>
       </c>
       <c r="BY22" t="n">
-        <v>0.7250087209966319</v>
+        <v>669</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.6765559189074467</v>
+        <v>669</v>
       </c>
       <c r="CA22" t="n">
-        <v>0.7407465090357149</v>
+        <v>669</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.7853553678572189</v>
+        <v>669</v>
+      </c>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>520.0509999999999</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>22.8005</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.496487114615601</v>
       </c>
       <c r="C23" t="n">
+        <v>2.261269787302956</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.525226471535845</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.261269787302956</v>
       </c>
       <c r="E23" t="n">
         <v>1.496487114615601</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01517225653688509</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.680186393168768</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1190079608128889</v>
+      </c>
       <c r="I23" t="n">
-        <v>11.45646000508652</v>
+        <v>0.09398208115884316</v>
       </c>
       <c r="J23" t="n">
-        <v>8.637699925236758</v>
+        <v>0.09976155783192558</v>
       </c>
       <c r="K23" t="n">
-        <v>8.141320319436407</v>
+        <v>0.1078144116916707</v>
       </c>
       <c r="L23" t="n">
-        <v>4.930053769720349</v>
+        <v>0.1258821504005778</v>
       </c>
       <c r="M23" t="n">
-        <v>6.773785212294002</v>
+        <v>0.1310474000224025</v>
       </c>
       <c r="N23" t="n">
-        <v>4.187291017734609</v>
+        <v>0.1268764421748473</v>
       </c>
       <c r="O23" t="n">
-        <v>5.615941585432465</v>
+        <v>0.111921024787453</v>
       </c>
       <c r="P23" t="n">
-        <v>3.508087385419194</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.898100734986111</v>
-      </c>
+        <v>0.1158435878333594</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>3.746401889144229</v>
+        <v>11.45507219302299</v>
       </c>
       <c r="S23" t="n">
-        <v>4.812880693398965</v>
+        <v>8.639245581098288</v>
       </c>
       <c r="T23" t="n">
-        <v>4.159759482266651</v>
+        <v>8.140942270562514</v>
       </c>
       <c r="U23" t="n">
-        <v>4.091130988006876</v>
+        <v>4.929767235884469</v>
       </c>
       <c r="V23" t="n">
-        <v>3.950205758987378</v>
+        <v>6.773542861364112</v>
       </c>
       <c r="W23" t="n">
-        <v>3.842125579953668</v>
+        <v>4.185987244429481</v>
       </c>
       <c r="X23" t="n">
-        <v>3.692293483086564</v>
+        <v>5.615977465654292</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.53411573413808</v>
+        <v>3.507502147652867</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.616450681125067</v>
+        <v>4.899021894859791</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.74623024554439</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>4.812606362460996</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.159743033561468</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.091442256325047</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>3.949839803547001</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>3.842385326851006</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.692436793458246</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.532604376973245</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.616883617876467</v>
       </c>
       <c r="AJ23" t="n">
-        <v>6.632522913444657</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>5.339728895586615</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.871290550592263</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>6.633296771035617</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.339958086766322</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.870859942448296</v>
+      </c>
+      <c r="AV23" t="n">
         <v>4.622338323721819</v>
       </c>
-      <c r="AN23" t="n">
-        <v>4.263067200861888</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>3.902794104996277</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>3.721198939327576</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.483340783170064</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>3.147165757095046</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.96358126873461</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.613424906990961</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.42624279783243</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.224819088405531</v>
-      </c>
       <c r="AW23" t="n">
-        <v>2.027218610860415</v>
+        <v>4.262770781644508</v>
       </c>
       <c r="AX23" t="n">
-        <v>2.147468561782241</v>
+        <v>3.902310078321355</v>
       </c>
       <c r="AY23" t="n">
-        <v>2.183222968559199</v>
+        <v>3.720361435469185</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.254019391240913</v>
+        <v>3.483145734896305</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.25680194888984</v>
+        <v>3.147775990157269</v>
       </c>
       <c r="BB23" t="n">
+        <v>2.964118534102596</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.612864127230581</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.427095730335028</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>2.224312726498493</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.027356069263352</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>2.146828444105642</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>2.183137469452237</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.255233620760946</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>2.255850580624804</v>
+      </c>
+      <c r="BK23" t="n">
         <v>8.75559971194375</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>8.75559971194375</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>8.75559971194375</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>8.75559971194375</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>8.75559971194375</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>8.75559971194375</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>8.75559971194375</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>8.75559971194375</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>8.75559971194375</v>
       </c>
-      <c r="BK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>0</v>
-      </c>
       <c r="BT23" t="n">
-        <v>0.2456710321670299</v>
+        <v>0</v>
       </c>
       <c r="BU23" t="n">
-        <v>0.2765266164457278</v>
+        <v>0</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.2567251886580743</v>
+        <v>0</v>
       </c>
       <c r="BW23" t="n">
-        <v>0.1756372999310831</v>
+        <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>0.1451939414493644</v>
+        <v>0</v>
       </c>
       <c r="BY23" t="n">
-        <v>0.2081533881501474</v>
+        <v>0</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.3115213021221911</v>
+        <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>0.2816284315252808</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="n">
-        <v>0.2154844514738312</v>
+        <v>0</v>
+      </c>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>3.532604376973245</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>3.616883617876467</v>
       </c>
     </row>
   </sheetData>
